--- a/tcm_data.xlsx
+++ b/tcm_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/055d7278b9591774/Desktop/clinic app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_2B59D2BFD380D3C2C73E6970441510344D078D0F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E38496A5-4C3F-4A2A-A9E4-448F9AE6E505}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_2B59D2BFD370D730B963C1F0504F98B47FBDF5AF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53FEC5CC-8D81-4E03-83F8-7C8096D88D8F}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="16200" windowHeight="9308" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="1177" windowWidth="16200" windowHeight="9308" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>藥名</t>
   </si>
@@ -35,15 +35,48 @@
   </si>
   <si>
     <t>附子理中丸</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>七寶美髯丹</t>
   </si>
   <si>
     <t>腎氣丸</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>溫補腎氣丸</t>
+  </si>
+  <si>
+    <t>杞菊地黃丸</t>
+  </si>
+  <si>
+    <t>濟生腎氣丸</t>
+  </si>
+  <si>
+    <t>知柏地黃丸</t>
+  </si>
+  <si>
+    <t>大黃蟅蟲丸</t>
+  </si>
+  <si>
+    <t>桂枝茯苓丸</t>
   </si>
   <si>
     <t>逍遙散</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>當歸芍藥散</t>
+  </si>
+  <si>
+    <t>補中益氣散</t>
+  </si>
+  <si>
+    <t>天灸粉</t>
+  </si>
+  <si>
+    <t>四黃膏</t>
+  </si>
+  <si>
+    <t>紫雲膏</t>
   </si>
 </sst>
 </file>
@@ -390,7 +423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
@@ -412,10 +445,10 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="C2">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="D2">
         <v>15</v>
@@ -426,10 +459,10 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C3">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D3">
         <v>15</v>
@@ -440,13 +473,181 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>1.9</v>
+        <v>38</v>
       </c>
       <c r="C4">
-        <v>500</v>
+        <v>5</v>
       </c>
       <c r="D4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>59</v>
+      </c>
+      <c r="C5">
+        <v>43</v>
+      </c>
+      <c r="D5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>38</v>
+      </c>
+      <c r="C6">
+        <v>23</v>
+      </c>
+      <c r="D6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>40</v>
+      </c>
+      <c r="C7">
+        <v>14</v>
+      </c>
+      <c r="D7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>38</v>
+      </c>
+      <c r="C8">
+        <v>56</v>
+      </c>
+      <c r="D8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>46</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10">
+        <v>36</v>
+      </c>
+      <c r="C10">
+        <v>75</v>
+      </c>
+      <c r="D10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11">
+        <v>41</v>
+      </c>
+      <c r="D11">
         <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="C12">
+        <v>334</v>
+      </c>
+      <c r="D12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13">
+        <v>6.13</v>
+      </c>
+      <c r="C13">
+        <v>55</v>
+      </c>
+      <c r="D13">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14">
+        <v>2.8</v>
+      </c>
+      <c r="C14">
+        <v>225</v>
+      </c>
+      <c r="D14">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15">
+        <v>150</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16">
+        <v>165</v>
+      </c>
+      <c r="C16">
+        <v>7</v>
+      </c>
+      <c r="D16">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/tcm_data.xlsx
+++ b/tcm_data.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/055d7278b9591774/Desktop/clinic app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_2B59D2BFD370D730B963C1F0504F98B47FBDF5AF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53FEC5CC-8D81-4E03-83F8-7C8096D88D8F}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="11_2B59D2BFD370D730B963C1F0504F98B47FBDF5AF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0DB83C8-5A7E-460E-8644-905B775EFD79}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="1177" windowWidth="16200" windowHeight="9308" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -136,6 +149,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -448,7 +465,7 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D2">
         <v>15</v>
@@ -462,7 +479,7 @@
         <v>35</v>
       </c>
       <c r="C3">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D3">
         <v>15</v>
@@ -476,7 +493,7 @@
         <v>38</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="D4">
         <v>15</v>
@@ -504,7 +521,7 @@
         <v>38</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="D6">
         <v>15</v>
@@ -518,7 +535,7 @@
         <v>40</v>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="D7">
         <v>15</v>
@@ -532,7 +549,7 @@
         <v>38</v>
       </c>
       <c r="C8">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D8">
         <v>15</v>
@@ -546,7 +563,7 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="D9">
         <v>15</v>
@@ -560,7 +577,7 @@
         <v>36</v>
       </c>
       <c r="C10">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D10">
         <v>15</v>
@@ -574,7 +591,7 @@
         <v>4</v>
       </c>
       <c r="C11">
-        <v>41</v>
+        <v>541</v>
       </c>
       <c r="D11">
         <v>50</v>

--- a/tcm_data.xlsx
+++ b/tcm_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/055d7278b9591774/Desktop/clinic app/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/055D7278B9591774/Desktop/clinic app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_2B59D2BFD370D730B963C1F0504F98B47FBDF5AF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0DB83C8-5A7E-460E-8644-905B775EFD79}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_2B59D2BFD370D730B963C1F0504F98B47FBDF5AF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57DF8B15-06C0-4C35-80A3-E5D5D03035BC}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -493,7 +493,7 @@
         <v>38</v>
       </c>
       <c r="C4">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D4">
         <v>15</v>
@@ -521,7 +521,7 @@
         <v>38</v>
       </c>
       <c r="C6">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="D6">
         <v>15</v>

--- a/tcm_data.xlsx
+++ b/tcm_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/055D7278B9591774/Desktop/clinic app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_2B59D2BFD370D730B963C1F0504F98B47FBDF5AF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57DF8B15-06C0-4C35-80A3-E5D5D03035BC}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_2B59D2BFD370D730B963C1F0504F98B47FBDF5AF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70DA23E9-D22B-42EC-8618-3359454255B3}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -479,7 +479,7 @@
         <v>35</v>
       </c>
       <c r="C3">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D3">
         <v>15</v>
@@ -521,7 +521,7 @@
         <v>38</v>
       </c>
       <c r="C6">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D6">
         <v>15</v>
@@ -563,7 +563,7 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D9">
         <v>15</v>
